--- a/content/knowledge-graph/templates/teacher-knowledge-graph-v2.xlsx
+++ b/content/knowledge-graph/templates/teacher-knowledge-graph-v2.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="1" r:id="R31509a500abb4895"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phenomena" sheetId="2" r:id="R3e638a228b314b80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KnowledgeResources" sheetId="3" r:id="R0a0c4a941db74d66"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NegotiationStrategies" sheetId="4" r:id="Ree13164d4f8d400f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GraphRelations(Edges)" sheetId="5" r:id="R78499357ebe4420e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scaffolds" sheetId="6" r:id="R5ec74c04049e42f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rubrics" sheetId="7" r:id="Rc9e03e8a2af14659"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outcomes" sheetId="8" r:id="Rbcb2696ebdb64f9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LearningContent" sheetId="9" r:id="R2e0e27418adf4cf2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="1" r:id="Rb701b2ae2151497d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phenomena" sheetId="2" r:id="R20eb3b96f2cc4c2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KnowledgeResources" sheetId="3" r:id="R9520a2de21d749b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NegotiationStrategies" sheetId="4" r:id="R40fa202a28ab44e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GraphRelations(Edges)" sheetId="5" r:id="R1039660e33ed4945"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scaffolds" sheetId="6" r:id="R973ec25e0fb04dde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rubrics" sheetId="7" r:id="Rb9b7839d5d68403e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outcomes" sheetId="8" r:id="R05c6e553167d4971"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LearningContent" sheetId="9" r:id="R3bf397b684a94b8f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -43,7 +43,7 @@
       <x:name val="Calibri"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -60,6 +60,11 @@
         <x:fgColor rgb="FF2F5597"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2F5597"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -67,7 +72,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="13">
+  <x:cellXfs count="17">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
@@ -104,6 +109,18 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -407,6 +424,7 @@
     <x:col min="9" max="9" width="45" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="12" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -449,6 +467,9 @@
       <x:c r="K1" s="12" t="str">
         <x:v>Difficulty</x:v>
       </x:c>
+      <x:c r="L1" s="16" t="str">
+        <x:v>ShortNameZH</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="5" t="inlineStr">
@@ -490,6 +511,9 @@
       <x:c r="K2" s="7" t="str">
         <x:v>基础</x:v>
       </x:c>
+      <x:c r="L2" s="4" t="str">
+        <x:v>初次接触索取目录</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="5" t="inlineStr">
@@ -531,6 +555,9 @@
       <x:c r="K3" s="7" t="str">
         <x:v>标准</x:v>
       </x:c>
+      <x:c r="L3" s="4" t="str">
+        <x:v>发出具体询盘</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="5" t="inlineStr">
@@ -572,6 +599,9 @@
       <x:c r="K4" s="7" t="str">
         <x:v>标准</x:v>
       </x:c>
+      <x:c r="L4" s="4" t="str">
+        <x:v>催询与条件探询</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="5" t="inlineStr">
@@ -613,6 +643,9 @@
       <x:c r="K5" s="7" t="str">
         <x:v>标准</x:v>
       </x:c>
+      <x:c r="L5" s="4" t="str">
+        <x:v>识别虚盘并催实盘</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="5" t="inlineStr">
@@ -654,6 +687,9 @@
       <x:c r="K6" s="7" t="str">
         <x:v>标准</x:v>
       </x:c>
+      <x:c r="L6" s="4" t="str">
+        <x:v>审核实盘条款</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="5" t="inlineStr">
@@ -695,6 +731,9 @@
       <x:c r="K7" s="7" t="str">
         <x:v>挑战</x:v>
       </x:c>
+      <x:c r="L7" s="4" t="str">
+        <x:v>价格还盘攻防</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="5" t="inlineStr">
@@ -736,6 +775,9 @@
       <x:c r="K8" s="7" t="str">
         <x:v>挑战</x:v>
       </x:c>
+      <x:c r="L8" s="4" t="str">
+        <x:v>付款与交期磋商</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="5" t="inlineStr">
@@ -777,6 +819,9 @@
       <x:c r="K9" s="7" t="str">
         <x:v>挑战</x:v>
       </x:c>
+      <x:c r="L9" s="4" t="str">
+        <x:v>有条件接受与成交</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="5" t="inlineStr">
@@ -818,6 +863,9 @@
       <x:c r="K10" s="7" t="str">
         <x:v>标准</x:v>
       </x:c>
+      <x:c r="L10" s="4" t="str">
+        <x:v>确认成交</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="5" t="inlineStr">
@@ -859,6 +907,9 @@
       <x:c r="K11" s="7" t="str">
         <x:v>标准</x:v>
       </x:c>
+      <x:c r="L11" s="4" t="str">
+        <x:v>催开信用证</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="5" t="inlineStr">
@@ -900,6 +951,9 @@
       <x:c r="K12" s="7" t="str">
         <x:v>标准</x:v>
       </x:c>
+      <x:c r="L12" s="4" t="str">
+        <x:v>包装与唛头磋商</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="5" t="inlineStr">
@@ -941,6 +995,9 @@
       <x:c r="K13" s="7" t="str">
         <x:v>挑战</x:v>
       </x:c>
+      <x:c r="L13" s="4" t="str">
+        <x:v>分批转船与催装</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="5" t="inlineStr">
@@ -982,6 +1039,9 @@
       <x:c r="K14" s="7" t="str">
         <x:v>挑战</x:v>
       </x:c>
+      <x:c r="L14" s="4" t="str">
+        <x:v>信用证审核改证</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="5" t="inlineStr">
@@ -1023,6 +1083,9 @@
       <x:c r="K15" s="7" t="str">
         <x:v>标准</x:v>
       </x:c>
+      <x:c r="L15" s="4" t="str">
+        <x:v>交单结汇与装运通知</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="5" t="inlineStr">
@@ -1064,6 +1127,9 @@
       <x:c r="K16" s="7" t="str">
         <x:v>挑战</x:v>
       </x:c>
+      <x:c r="L16" s="4" t="str">
+        <x:v>检验条款磋商</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="5" t="inlineStr">
@@ -1105,6 +1171,9 @@
       <x:c r="K17" s="7" t="str">
         <x:v>挑战</x:v>
       </x:c>
+      <x:c r="L17" s="4" t="str">
+        <x:v>保险险别磋商</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="5" t="inlineStr">
@@ -1146,6 +1215,9 @@
       <x:c r="K18" s="7" t="str">
         <x:v>挑战</x:v>
       </x:c>
+      <x:c r="L18" s="4" t="str">
+        <x:v>仲裁条款磋商</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="5" t="inlineStr">
@@ -1187,6 +1259,9 @@
       <x:c r="K19" s="7" t="str">
         <x:v>挑战</x:v>
       </x:c>
+      <x:c r="L19" s="4" t="str">
+        <x:v>提出质量索赔</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="5" t="inlineStr">
@@ -1228,6 +1303,9 @@
       <x:c r="K20" s="7" t="str">
         <x:v>挑战</x:v>
       </x:c>
+      <x:c r="L20" s="4" t="str">
+        <x:v>应对卖方抗辩</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="5" t="inlineStr">
@@ -1268,6 +1346,9 @@
       </x:c>
       <x:c r="K21" s="7" t="str">
         <x:v>挑战</x:v>
+      </x:c>
+      <x:c r="L21" s="4" t="str">
+        <x:v>理赔和解</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1287,6 +1368,7 @@
     <x:col min="6" max="6" width="10" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -1322,6 +1404,9 @@
       <x:c r="H1" s="12" t="str">
         <x:v>DynamicTrigger</x:v>
       </x:c>
+      <x:c r="I1" s="16" t="str">
+        <x:v>ShortNameZH</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="5" t="inlineStr">
@@ -1356,6 +1441,9 @@
       <x:c r="H2" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
+      <x:c r="I2" s="4" t="str">
+        <x:v>首函结构不完整</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="5" t="inlineStr">
@@ -1390,6 +1478,9 @@
       <x:c r="H3" s="7" t="str">
         <x:v>是</x:v>
       </x:c>
+      <x:c r="I3" s="4" t="str">
+        <x:v>过早披露与过度承诺</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="5" t="inlineStr">
@@ -1424,6 +1515,9 @@
       <x:c r="H4" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
+      <x:c r="I4" s="4" t="str">
+        <x:v>询盘要素不完整</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="5" t="inlineStr">
@@ -1458,6 +1552,9 @@
       <x:c r="H5" s="7" t="str">
         <x:v>是</x:v>
       </x:c>
+      <x:c r="I5" s="4" t="str">
+        <x:v>泄露保留价</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="5" t="inlineStr">
@@ -1492,6 +1589,9 @@
       <x:c r="H6" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
+      <x:c r="I6" s="4" t="str">
+        <x:v>合理催询时机</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="5" t="inlineStr">
@@ -1526,6 +1626,9 @@
       <x:c r="H7" s="7" t="str">
         <x:v>是</x:v>
       </x:c>
+      <x:c r="I7" s="4" t="str">
+        <x:v>虚构紧迫性</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="5" t="inlineStr">
@@ -1560,6 +1663,9 @@
       <x:c r="H8" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
+      <x:c r="I8" s="4" t="str">
+        <x:v>将虚盘误作实盘</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="5" t="inlineStr">
@@ -1594,6 +1700,9 @@
       <x:c r="H9" s="7" t="str">
         <x:v>是</x:v>
       </x:c>
+      <x:c r="I9" s="4" t="str">
+        <x:v>未要求实盘与有效期</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="5" t="inlineStr">
@@ -1628,6 +1737,9 @@
       <x:c r="H10" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
+      <x:c r="I10" s="4" t="str">
+        <x:v>未核验实盘要素</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="5" t="inlineStr">
@@ -1662,6 +1774,9 @@
       <x:c r="H11" s="7" t="str">
         <x:v>是</x:v>
       </x:c>
+      <x:c r="I11" s="4" t="str">
+        <x:v>修改构成还盘</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="5" t="inlineStr">
@@ -1696,6 +1811,9 @@
       <x:c r="H12" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
+      <x:c r="I12" s="4" t="str">
+        <x:v>虚构竞品报价锚定</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="5" t="inlineStr">
@@ -1730,6 +1848,9 @@
       <x:c r="H13" s="7" t="str">
         <x:v>是</x:v>
       </x:c>
+      <x:c r="I13" s="4" t="str">
+        <x:v>价格转向条件交换</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="5" t="inlineStr">
@@ -1764,6 +1885,9 @@
       <x:c r="H14" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
+      <x:c r="I14" s="4" t="str">
+        <x:v>忽视卖方首单风险</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="5" t="inlineStr">
@@ -1798,6 +1922,9 @@
       <x:c r="H15" s="7" t="str">
         <x:v>是</x:v>
       </x:c>
+      <x:c r="I15" s="4" t="str">
+        <x:v>买卖交期错位</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="5" t="inlineStr">
@@ -1832,6 +1959,9 @@
       <x:c r="H16" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
+      <x:c r="I16" s="4" t="str">
+        <x:v>非价格让步评估</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="5" t="inlineStr">
@@ -1866,6 +1996,9 @@
       <x:c r="H17" s="7" t="str">
         <x:v>是</x:v>
       </x:c>
+      <x:c r="I17" s="4" t="str">
+        <x:v>口头承诺未书面化</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="5" t="inlineStr">
@@ -1900,6 +2033,9 @@
       <x:c r="H18" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
+      <x:c r="I18" s="4" t="str">
+        <x:v>书面与口头约定不符</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="5" t="inlineStr">
@@ -1934,6 +2070,9 @@
       <x:c r="H19" s="7" t="str">
         <x:v>是</x:v>
       </x:c>
+      <x:c r="I19" s="4" t="str">
+        <x:v>未澄清即签署</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="5" t="inlineStr">
@@ -1968,6 +2107,9 @@
       <x:c r="H20" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
+      <x:c r="I20" s="4" t="str">
+        <x:v>内部延误威胁交期</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="5" t="inlineStr">
@@ -2002,6 +2144,9 @@
       <x:c r="H21" s="7" t="str">
         <x:v>是</x:v>
       </x:c>
+      <x:c r="I21" s="4" t="str">
+        <x:v>承诺无把握的开证日</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="5" t="inlineStr">
@@ -2036,6 +2181,9 @@
       <x:c r="H22" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
+      <x:c r="I22" s="4" t="str">
+        <x:v>包装防护不足</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="5" t="inlineStr">
@@ -2070,6 +2218,9 @@
       <x:c r="H23" s="7" t="str">
         <x:v>是</x:v>
       </x:c>
+      <x:c r="I23" s="4" t="str">
+        <x:v>过度包装要求</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="5" t="inlineStr">
@@ -2104,6 +2255,9 @@
       <x:c r="H24" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
+      <x:c r="I24" s="4" t="str">
+        <x:v>分批装运权衡</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="5" t="inlineStr">
@@ -2138,6 +2292,9 @@
       <x:c r="H25" s="7" t="str">
         <x:v>是</x:v>
       </x:c>
+      <x:c r="I25" s="4" t="str">
+        <x:v>转船需同步改证</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="5" t="inlineStr">
@@ -2172,6 +2329,9 @@
       <x:c r="H26" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
+      <x:c r="I26" s="4" t="str">
+        <x:v>改证超出合同</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="5" t="inlineStr">
@@ -2206,6 +2366,9 @@
       <x:c r="H27" s="7" t="str">
         <x:v>是</x:v>
       </x:c>
+      <x:c r="I27" s="4" t="str">
+        <x:v>合理运营性改证</x:v>
+      </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="5" t="inlineStr">
@@ -2240,6 +2403,9 @@
       <x:c r="H28" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
+      <x:c r="I28" s="4" t="str">
+        <x:v>货未到即拒付</x:v>
+      </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="5" t="inlineStr">
@@ -2274,6 +2440,9 @@
       <x:c r="H29" s="7" t="str">
         <x:v>是</x:v>
       </x:c>
+      <x:c r="I29" s="4" t="str">
+        <x:v>单据疑点核验</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="5" t="inlineStr">
@@ -2308,6 +2477,9 @@
       <x:c r="H30" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
+      <x:c r="I30" s="4" t="str">
+        <x:v>装港检验终局性争议</x:v>
+      </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="5" t="inlineStr">
@@ -2342,6 +2514,9 @@
       <x:c r="H31" s="7" t="str">
         <x:v>是</x:v>
       </x:c>
+      <x:c r="I31" s="4" t="str">
+        <x:v>制造缺陷与运输损伤</x:v>
+      </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="5" t="inlineStr">
@@ -2376,6 +2551,9 @@
       <x:c r="H32" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
+      <x:c r="I32" s="4" t="str">
+        <x:v>CIF最低保险范围</x:v>
+      </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="5" t="inlineStr">
@@ -2410,6 +2588,9 @@
       <x:c r="H33" s="7" t="str">
         <x:v>是</x:v>
       </x:c>
+      <x:c r="I33" s="4" t="str">
+        <x:v>扩大险别与保费分担</x:v>
+      </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="5" t="inlineStr">
@@ -2444,6 +2625,9 @@
       <x:c r="H34" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
+      <x:c r="I34" s="4" t="str">
+        <x:v>争议解决机制不明</x:v>
+      </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="5" t="inlineStr">
@@ -2478,6 +2662,9 @@
       <x:c r="H35" s="7" t="str">
         <x:v>是</x:v>
       </x:c>
+      <x:c r="I35" s="4" t="str">
+        <x:v>多重救济路径冲突</x:v>
+      </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="5" t="inlineStr">
@@ -2512,6 +2699,9 @@
       <x:c r="H36" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
+      <x:c r="I36" s="4" t="str">
+        <x:v>质量与运输损失分流</x:v>
+      </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="5" t="inlineStr">
@@ -2546,6 +2736,9 @@
       <x:c r="H37" s="7" t="str">
         <x:v>是</x:v>
       </x:c>
+      <x:c r="I37" s="4" t="str">
+        <x:v>重复索赔风险</x:v>
+      </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="5" t="inlineStr">
@@ -2580,6 +2773,9 @@
       <x:c r="H38" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
+      <x:c r="I38" s="4" t="str">
+        <x:v>公差与抽样争议</x:v>
+      </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="5" t="inlineStr">
@@ -2614,6 +2810,9 @@
       <x:c r="H39" s="7" t="str">
         <x:v>是</x:v>
       </x:c>
+      <x:c r="I39" s="4" t="str">
+        <x:v>证据不足需联合复检</x:v>
+      </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="5" t="inlineStr">
@@ -2648,6 +2847,9 @@
       <x:c r="H40" s="7" t="str">
         <x:v>否</x:v>
       </x:c>
+      <x:c r="I40" s="4" t="str">
+        <x:v>非现金和解评估</x:v>
+      </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="5" t="inlineStr">
@@ -2681,6 +2883,9 @@
       </x:c>
       <x:c r="H41" s="7" t="str">
         <x:v>是</x:v>
+      </x:c>
+      <x:c r="I41" s="4" t="str">
+        <x:v>和解捆绑未来订单</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2700,6 +2905,7 @@
     <x:col min="6" max="6" width="26" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -2737,6 +2943,9 @@
       <x:c r="H1" s="12" t="str">
         <x:v>DisplayTiming</x:v>
       </x:c>
+      <x:c r="I1" s="16" t="str">
+        <x:v>ShortNameZH</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="5" t="inlineStr">
@@ -2771,6 +2980,9 @@
       <x:c r="H2" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I2" s="4" t="str">
+        <x:v>CIF术语</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="5" t="inlineStr">
@@ -2805,6 +3017,9 @@
       <x:c r="H3" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I3" s="4" t="str">
+        <x:v>即期信用证</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="5" t="inlineStr">
@@ -2839,6 +3054,9 @@
       <x:c r="H4" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I4" s="4" t="str">
+        <x:v>实盘</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="5" t="inlineStr">
@@ -2873,6 +3091,9 @@
       <x:c r="H5" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I5" s="4" t="str">
+        <x:v>虚盘</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="5" t="inlineStr">
@@ -2907,6 +3128,9 @@
       <x:c r="H6" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I6" s="4" t="str">
+        <x:v>还盘</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="5" t="inlineStr">
@@ -2941,6 +3165,9 @@
       <x:c r="H7" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I7" s="4" t="str">
+        <x:v>报盘有效期</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="5" t="inlineStr">
@@ -2975,6 +3202,9 @@
       <x:c r="H8" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I8" s="4" t="str">
+        <x:v>试订单</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="5" t="inlineStr">
@@ -3009,6 +3239,9 @@
       <x:c r="H9" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I9" s="4" t="str">
+        <x:v>分批装运</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="5" t="inlineStr">
@@ -3043,6 +3276,9 @@
       <x:c r="H10" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I10" s="4" t="str">
+        <x:v>转船</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="5" t="inlineStr">
@@ -3077,6 +3313,9 @@
       <x:c r="H11" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I11" s="4" t="str">
+        <x:v>协会货物保险条款</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="5" t="inlineStr">
@@ -3111,6 +3350,9 @@
       <x:c r="H12" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I12" s="4" t="str">
+        <x:v>CCIC检验证书</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="5" t="inlineStr">
@@ -3145,6 +3387,9 @@
       <x:c r="H13" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I13" s="4" t="str">
+        <x:v>销售确认书</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="5" t="inlineStr">
@@ -3179,6 +3424,9 @@
       <x:c r="H14" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I14" s="4" t="str">
+        <x:v>交单期</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="5" t="inlineStr">
@@ -3213,6 +3461,9 @@
       <x:c r="H15" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I15" s="4" t="str">
+        <x:v>隐蔽缺陷与表面缺陷</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="5" t="inlineStr">
@@ -3247,6 +3498,9 @@
       <x:c r="H16" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I16" s="4" t="str">
+        <x:v>BATNA谈判替代方案</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="5" t="inlineStr">
@@ -3281,6 +3535,9 @@
       <x:c r="H17" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I17" s="4" t="str">
+        <x:v>CIF风险费用划分</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="5" t="inlineStr">
@@ -3315,6 +3572,9 @@
       <x:c r="H18" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I18" s="4" t="str">
+        <x:v>信用证单据交易原则</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="5" t="inlineStr">
@@ -3349,6 +3609,9 @@
       <x:c r="H19" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I19" s="4" t="str">
+        <x:v>UCP600分批装运规则</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="5" t="inlineStr">
@@ -3383,6 +3646,9 @@
       <x:c r="H20" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I20" s="4" t="str">
+        <x:v>CISG镜像规则与还盘</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="5" t="inlineStr">
@@ -3417,6 +3683,9 @@
       <x:c r="H21" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I21" s="4" t="str">
+        <x:v>信用证严格相符原则</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="5" t="inlineStr">
@@ -3451,6 +3720,9 @@
       <x:c r="H22" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I22" s="4" t="str">
+        <x:v>货物保险条款范围</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="5" t="inlineStr">
@@ -3485,6 +3757,9 @@
       <x:c r="H23" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I23" s="4" t="str">
+        <x:v>检验证书终局条款</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="5" t="inlineStr">
@@ -3519,6 +3794,9 @@
       <x:c r="H24" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I24" s="4" t="str">
+        <x:v>争议解决条款效力</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="5" t="inlineStr">
@@ -3553,6 +3831,9 @@
       <x:c r="H25" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I25" s="4" t="str">
+        <x:v>售后条款书面确认</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="5" t="inlineStr">
@@ -3587,6 +3868,9 @@
       <x:c r="H26" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I26" s="4" t="str">
+        <x:v>信用证修改程序</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="5" t="inlineStr">
@@ -3621,6 +3905,9 @@
       <x:c r="H27" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I27" s="4" t="str">
+        <x:v>包装唛头适当标准</x:v>
+      </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="5" t="inlineStr">
@@ -3655,6 +3942,9 @@
       <x:c r="H28" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I28" s="4" t="str">
+        <x:v>CISG不符通知规则</x:v>
+      </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="5" t="inlineStr">
@@ -3689,6 +3979,9 @@
       <x:c r="H29" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I29" s="4" t="str">
+        <x:v>质量索赔举证责任</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="5" t="inlineStr">
@@ -3723,6 +4016,9 @@
       <x:c r="H30" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I30" s="4" t="str">
+        <x:v>报盘撤回撤销规则</x:v>
+      </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="5" t="inlineStr">
@@ -3757,6 +4053,9 @@
       <x:c r="H31" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I31" s="4" t="str">
+        <x:v>保留价保密</x:v>
+      </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="5" t="inlineStr">
@@ -3791,6 +4090,9 @@
       <x:c r="H32" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I32" s="4" t="str">
+        <x:v>商务询盘函结构</x:v>
+      </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="5" t="inlineStr">
@@ -3825,6 +4127,9 @@
       <x:c r="H33" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I33" s="4" t="str">
+        <x:v>实盘函核心要素</x:v>
+      </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="5" t="inlineStr">
@@ -3859,6 +4164,9 @@
       <x:c r="H34" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I34" s="4" t="str">
+        <x:v>销售确认书核心条款</x:v>
+      </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="5" t="inlineStr">
@@ -3893,6 +4201,9 @@
       <x:c r="H35" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I35" s="4" t="str">
+        <x:v>商业发票</x:v>
+      </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="5" t="inlineStr">
@@ -3927,6 +4238,9 @@
       <x:c r="H36" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I36" s="4" t="str">
+        <x:v>装箱单</x:v>
+      </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="5" t="inlineStr">
@@ -3961,6 +4275,9 @@
       <x:c r="H37" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I37" s="4" t="str">
+        <x:v>清洁与指示提单</x:v>
+      </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="5" t="inlineStr">
@@ -3995,6 +4312,9 @@
       <x:c r="H38" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I38" s="4" t="str">
+        <x:v>原产地证书</x:v>
+      </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="5" t="inlineStr">
@@ -4029,6 +4349,9 @@
       <x:c r="H39" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I39" s="4" t="str">
+        <x:v>保险单据</x:v>
+      </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="5" t="inlineStr">
@@ -4063,6 +4386,9 @@
       <x:c r="H40" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I40" s="4" t="str">
+        <x:v>开证申请与单据清单</x:v>
+      </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="5" t="inlineStr">
@@ -4097,6 +4423,9 @@
       <x:c r="H41" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I41" s="4" t="str">
+        <x:v>CCIC检验证书内容</x:v>
+      </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="5" t="inlineStr">
@@ -4131,6 +4460,9 @@
       <x:c r="H42" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I42" s="4" t="str">
+        <x:v>索赔函与证据附件</x:v>
+      </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="5" t="inlineStr">
@@ -4165,6 +4497,9 @@
       <x:c r="H43" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I43" s="4" t="str">
+        <x:v>信用证改证函</x:v>
+      </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="5" t="inlineStr">
@@ -4199,6 +4534,9 @@
       <x:c r="H44" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I44" s="4" t="str">
+        <x:v>质保备件条款</x:v>
+      </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="5" t="inlineStr">
@@ -4233,6 +4571,9 @@
       <x:c r="H45" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I45" s="4" t="str">
+        <x:v>展会线索跟进流程</x:v>
+      </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="5" t="inlineStr">
@@ -4267,6 +4608,9 @@
       <x:c r="H46" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I46" s="4" t="str">
+        <x:v>询盘至接受循环</x:v>
+      </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="5" t="inlineStr">
@@ -4301,6 +4645,9 @@
       <x:c r="H47" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I47" s="4" t="str">
+        <x:v>开证流程</x:v>
+      </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="5" t="inlineStr">
@@ -4335,6 +4682,9 @@
       <x:c r="H48" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I48" s="4" t="str">
+        <x:v>装运与交单流程</x:v>
+      </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="5" t="inlineStr">
@@ -4369,6 +4719,9 @@
       <x:c r="H49" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I49" s="4" t="str">
+        <x:v>商检与索赔流程</x:v>
+      </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="5" t="inlineStr">
@@ -4403,6 +4756,9 @@
       <x:c r="H50" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I50" s="4" t="str">
+        <x:v>合同审核清单</x:v>
+      </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="5" t="inlineStr">
@@ -4437,6 +4793,9 @@
       <x:c r="H51" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I51" s="4" t="str">
+        <x:v>T/T与L/C结算流程</x:v>
+      </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="5" t="inlineStr">
@@ -4471,6 +4830,9 @@
       <x:c r="H52" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I52" s="4" t="str">
+        <x:v>争议解决升级流程</x:v>
+      </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="5" t="inlineStr">
@@ -4505,6 +4867,9 @@
       <x:c r="H53" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I53" s="4" t="str">
+        <x:v>订单确认与偏差澄清</x:v>
+      </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="5" t="inlineStr">
@@ -4539,6 +4904,9 @@
       <x:c r="H54" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I54" s="4" t="str">
+        <x:v>分批转船安排流程</x:v>
+      </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="5" t="inlineStr">
@@ -4573,6 +4941,9 @@
       <x:c r="H55" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I55" s="4" t="str">
+        <x:v>投保与保费支付流程</x:v>
+      </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="5" t="inlineStr">
@@ -4607,6 +4978,9 @@
       <x:c r="H56" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I56" s="4" t="str">
+        <x:v>售后与质保索赔流程</x:v>
+      </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="5" t="inlineStr">
@@ -4641,6 +5015,9 @@
       <x:c r="H57" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I57" s="4" t="str">
+        <x:v>商务邮件礼仪</x:v>
+      </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="5" t="inlineStr">
@@ -4675,6 +5052,9 @@
       <x:c r="H58" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I58" s="4" t="str">
+        <x:v>价格谈判锚定技巧</x:v>
+      </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="5" t="inlineStr">
@@ -4709,6 +5089,9 @@
       <x:c r="H59" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I59" s="4" t="str">
+        <x:v>积极倾听与澄清提问</x:v>
+      </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="5" t="inlineStr">
@@ -4743,6 +5126,9 @@
       <x:c r="H60" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I60" s="4" t="str">
+        <x:v>避免过度承诺的模糊语</x:v>
+      </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="5" t="inlineStr">
@@ -4777,6 +5163,9 @@
       <x:c r="H61" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I61" s="4" t="str">
+        <x:v>坚定催复语气</x:v>
+      </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="5" t="inlineStr">
@@ -4811,6 +5200,9 @@
       <x:c r="H62" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I62" s="4" t="str">
+        <x:v>正向框架增值让步</x:v>
+      </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="5" t="inlineStr">
@@ -4845,6 +5237,9 @@
       <x:c r="H63" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I63" s="4" t="str">
+        <x:v>质量争议降级措辞</x:v>
+      </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="5" t="inlineStr">
@@ -4879,6 +5274,9 @@
       <x:c r="H64" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I64" s="4" t="str">
+        <x:v>书面确认请求礼仪</x:v>
+      </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="5" t="inlineStr">
@@ -4913,6 +5311,9 @@
       <x:c r="H65" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I65" s="4" t="str">
+        <x:v>首次合作信任措辞</x:v>
+      </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="5" t="inlineStr">
@@ -4947,6 +5348,9 @@
       <x:c r="H66" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I66" s="4" t="str">
+        <x:v>跨境谈判语域</x:v>
+      </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="5" t="inlineStr">
@@ -4981,6 +5385,9 @@
       <x:c r="H67" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I67" s="4" t="str">
+        <x:v>合理紧迫性表达</x:v>
+      </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="5" t="inlineStr">
@@ -5015,6 +5422,9 @@
       <x:c r="H68" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I68" s="4" t="str">
+        <x:v>最终成交收口技巧</x:v>
+      </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="5" t="inlineStr">
@@ -5049,6 +5459,9 @@
       <x:c r="H69" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I69" s="4" t="str">
+        <x:v>谈判选择性披露</x:v>
+      </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="5" t="inlineStr">
@@ -5083,6 +5496,9 @@
       <x:c r="H70" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I70" s="4" t="str">
+        <x:v>LED模组价格基准</x:v>
+      </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="5" t="inlineStr">
@@ -5117,6 +5533,9 @@
       <x:c r="H71" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I71" s="4" t="str">
+        <x:v>竞争格局认知</x:v>
+      </x:c>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="5" t="inlineStr">
@@ -5151,6 +5570,9 @@
       <x:c r="H72" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I72" s="4" t="str">
+        <x:v>航线交期趋势</x:v>
+      </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="5" t="inlineStr">
@@ -5185,6 +5607,9 @@
       <x:c r="H73" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I73" s="4" t="str">
+        <x:v>原材料成本波动</x:v>
+      </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="5" t="inlineStr">
@@ -5219,6 +5644,9 @@
       <x:c r="H74" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I74" s="4" t="str">
+        <x:v>季节性排产规律</x:v>
+      </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="5" t="inlineStr">
@@ -5253,6 +5681,9 @@
       <x:c r="H75" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I75" s="4" t="str">
+        <x:v>敏感电子品包装标准</x:v>
+      </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="5" t="inlineStr">
@@ -5287,6 +5718,9 @@
       <x:c r="H76" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I76" s="4" t="str">
+        <x:v>美元贸易汇率风险</x:v>
+      </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="5" t="inlineStr">
@@ -5321,6 +5755,9 @@
       <x:c r="H77" s="7" t="str">
         <x:v>需要时</x:v>
       </x:c>
+      <x:c r="I77" s="4" t="str">
+        <x:v>电子产品质保惯例</x:v>
+      </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="5" t="inlineStr">
@@ -5354,6 +5791,9 @@
       </x:c>
       <x:c r="H78" s="7" t="str">
         <x:v>需要时</x:v>
+      </x:c>
+      <x:c r="I78" s="4" t="str">
+        <x:v>货运保险保费认知</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5373,6 +5813,7 @@
     <x:col min="6" max="6" width="45" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="42" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="42" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -5410,6 +5851,9 @@
       <x:c r="H1" s="12" t="str">
         <x:v>ExpectedImpact</x:v>
       </x:c>
+      <x:c r="I1" s="16" t="str">
+        <x:v>ShortNameZH</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="5" t="inlineStr">
@@ -5440,6 +5884,9 @@
       <x:c r="F2" s="7" t="str"/>
       <x:c r="G2" s="7" t="str"/>
       <x:c r="H2" s="7" t="str"/>
+      <x:c r="I2" s="4" t="str">
+        <x:v>锚定策略</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="5" t="inlineStr">
@@ -5470,6 +5917,9 @@
       <x:c r="F3" s="7" t="str"/>
       <x:c r="G3" s="7" t="str"/>
       <x:c r="H3" s="7" t="str"/>
+      <x:c r="I3" s="4" t="str">
+        <x:v>区间折中收敛</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="5" t="inlineStr">
@@ -5500,6 +5950,9 @@
       <x:c r="F4" s="7" t="str"/>
       <x:c r="G4" s="7" t="str"/>
       <x:c r="H4" s="7" t="str"/>
+      <x:c r="I4" s="4" t="str">
+        <x:v>增值条件交换</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="5" t="inlineStr">
@@ -5530,6 +5983,9 @@
       <x:c r="F5" s="7" t="str"/>
       <x:c r="G5" s="7" t="str"/>
       <x:c r="H5" s="7" t="str"/>
+      <x:c r="I5" s="4" t="str">
+        <x:v>条件让步</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="5" t="inlineStr">
@@ -5560,6 +6016,9 @@
       <x:c r="F6" s="7" t="str"/>
       <x:c r="G6" s="7" t="str"/>
       <x:c r="H6" s="7" t="str"/>
+      <x:c r="I6" s="4" t="str">
+        <x:v>合理期限施压</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="5" t="inlineStr">
@@ -5590,6 +6049,9 @@
       <x:c r="F7" s="7" t="str"/>
       <x:c r="G7" s="7" t="str"/>
       <x:c r="H7" s="7" t="str"/>
+      <x:c r="I7" s="4" t="str">
+        <x:v>耐心与策略性沉默</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="5" t="inlineStr">
@@ -5620,6 +6082,9 @@
       <x:c r="F8" s="7" t="str"/>
       <x:c r="G8" s="7" t="str"/>
       <x:c r="H8" s="7" t="str"/>
+      <x:c r="I8" s="4" t="str">
+        <x:v>多议题打包谈判</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="5" t="inlineStr">
@@ -5650,6 +6115,9 @@
       <x:c r="F9" s="7" t="str"/>
       <x:c r="G9" s="7" t="str"/>
       <x:c r="H9" s="7" t="str"/>
+      <x:c r="I9" s="4" t="str">
+        <x:v>BATNA杠杆</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="5" t="inlineStr">
@@ -5680,6 +6148,9 @@
       <x:c r="F10" s="7" t="str"/>
       <x:c r="G10" s="7" t="str"/>
       <x:c r="H10" s="7" t="str"/>
+      <x:c r="I10" s="4" t="str">
+        <x:v>坚持书面确认</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="5" t="inlineStr">
@@ -5710,6 +6181,9 @@
       <x:c r="F11" s="7" t="str"/>
       <x:c r="G11" s="7" t="str"/>
       <x:c r="H11" s="7" t="str"/>
+      <x:c r="I11" s="4" t="str">
+        <x:v>事实型反驳</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="5" t="inlineStr">
@@ -5740,6 +6214,9 @@
       <x:c r="F12" s="7" t="str"/>
       <x:c r="G12" s="7" t="str"/>
       <x:c r="H12" s="7" t="str"/>
+      <x:c r="I12" s="4" t="str">
+        <x:v>折中各让一半</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="5" t="inlineStr">
@@ -5770,6 +6247,9 @@
       <x:c r="F13" s="7" t="str"/>
       <x:c r="G13" s="7" t="str"/>
       <x:c r="H13" s="7" t="str"/>
+      <x:c r="I13" s="4" t="str">
+        <x:v>互惠原则</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="5" t="inlineStr">
@@ -5800,6 +6280,9 @@
       <x:c r="F14" s="7" t="str"/>
       <x:c r="G14" s="7" t="str"/>
       <x:c r="H14" s="7" t="str"/>
+      <x:c r="I14" s="4" t="str">
+        <x:v>保留价信息控制</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="5" t="inlineStr">
@@ -5830,6 +6313,9 @@
       <x:c r="F15" s="7" t="str"/>
       <x:c r="G15" s="7" t="str"/>
       <x:c r="H15" s="7" t="str"/>
+      <x:c r="I15" s="4" t="str">
+        <x:v>新客户关系建立</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="5" t="inlineStr">
@@ -5860,6 +6346,9 @@
       <x:c r="F16" s="7" t="str"/>
       <x:c r="G16" s="7" t="str"/>
       <x:c r="H16" s="7" t="str"/>
+      <x:c r="I16" s="4" t="str">
+        <x:v>分级升级策略</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="5" t="inlineStr">
@@ -5890,6 +6379,9 @@
       <x:c r="F17" s="7" t="str"/>
       <x:c r="G17" s="7" t="str"/>
       <x:c r="H17" s="7" t="str"/>
+      <x:c r="I17" s="4" t="str">
+        <x:v>证据型索赔陈述</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="5" t="inlineStr">
@@ -5920,6 +6412,9 @@
       <x:c r="F18" s="7" t="str"/>
       <x:c r="G18" s="7" t="str"/>
       <x:c r="H18" s="7" t="str"/>
+      <x:c r="I18" s="4" t="str">
+        <x:v>联合核验提案</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="5" t="inlineStr">
@@ -5950,6 +6445,9 @@
       <x:c r="F19" s="7" t="str"/>
       <x:c r="G19" s="7" t="str"/>
       <x:c r="H19" s="7" t="str"/>
+      <x:c r="I19" s="4" t="str">
+        <x:v>改证审查策略</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="5" t="inlineStr">
@@ -5980,6 +6478,9 @@
       <x:c r="F20" s="7" t="str"/>
       <x:c r="G20" s="7" t="str"/>
       <x:c r="H20" s="7" t="str"/>
+      <x:c r="I20" s="4" t="str">
+        <x:v>风险适配包装谈判</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="5" t="inlineStr">
@@ -6010,6 +6511,9 @@
       <x:c r="F21" s="7" t="str"/>
       <x:c r="G21" s="7" t="str"/>
       <x:c r="H21" s="7" t="str"/>
+      <x:c r="I21" s="4" t="str">
+        <x:v>选择性披露</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="5" t="inlineStr">
@@ -6040,6 +6544,9 @@
       <x:c r="F22" s="7" t="str"/>
       <x:c r="G22" s="7" t="str"/>
       <x:c r="H22" s="7" t="str"/>
+      <x:c r="I22" s="4" t="str">
+        <x:v>实盘核验策略</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="5" t="inlineStr">
@@ -6070,6 +6577,9 @@
       <x:c r="F23" s="7" t="str"/>
       <x:c r="G23" s="7" t="str"/>
       <x:c r="H23" s="7" t="str"/>
+      <x:c r="I23" s="4" t="str">
+        <x:v>CISG合规还盘</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="5" t="inlineStr">
@@ -6100,6 +6610,9 @@
       <x:c r="F24" s="7" t="str"/>
       <x:c r="G24" s="7" t="str"/>
       <x:c r="H24" s="7" t="str"/>
+      <x:c r="I24" s="4" t="str">
+        <x:v>交期付款交换</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="5" t="inlineStr">
@@ -6130,6 +6643,9 @@
       <x:c r="F25" s="7" t="str"/>
       <x:c r="G25" s="7" t="str"/>
       <x:c r="H25" s="7" t="str"/>
+      <x:c r="I25" s="4" t="str">
+        <x:v>妥协和解策略</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="5" t="inlineStr">
@@ -6160,6 +6676,9 @@
       <x:c r="F26" s="7" t="str"/>
       <x:c r="G26" s="7" t="str"/>
       <x:c r="H26" s="7" t="str"/>
+      <x:c r="I26" s="4" t="str">
+        <x:v>专业降级策略</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
